--- a/assets/Матрица_компетенций_1С.xlsx
+++ b/assets/Матрица_компетенций_1С.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fsk\vdi\Folders\ukolovaaa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\probl\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC229BE0-6D43-4CFE-B498-108D4D6C9435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF2ED2B-4D66-4290-BD9A-1F1A4C5CC67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Перечень компетенций" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="103">
   <si>
     <t>Тип компетенции (Hard/Soft)</t>
   </si>
@@ -372,12 +372,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -532,128 +540,122 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -936,21 +938,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBBB767E-C84C-4CE4-8559-2D5C098FF150}">
   <dimension ref="A1:I54"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="40.44140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="58.5546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="17.6328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="40.453125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="58.54296875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.6328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="12.36328125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="11.453125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="11.36328125" style="5" customWidth="1"/>
+    <col min="10" max="16384" width="8.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -979,36 +981,36 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="40" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F2" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="27">
-        <v>2</v>
-      </c>
-      <c r="H2" s="27">
-        <v>3</v>
-      </c>
-      <c r="I2" s="27">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G2" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="25" t="s">
         <v>9</v>
       </c>
@@ -1021,23 +1023,23 @@
       <c r="D3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="41">
         <v>1</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="42">
         <v>1</v>
       </c>
-      <c r="G3" s="28">
-        <v>2</v>
-      </c>
-      <c r="H3" s="28">
-        <v>2</v>
-      </c>
-      <c r="I3" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G3" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="25" t="s">
         <v>9</v>
       </c>
@@ -1050,52 +1052,52 @@
       <c r="D4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="41">
         <v>1</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="42">
         <v>1</v>
       </c>
-      <c r="G4" s="28">
-        <v>2</v>
-      </c>
-      <c r="H4" s="28">
-        <v>2</v>
-      </c>
-      <c r="I4" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G4" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="45" t="s">
+      <c r="C5" s="40" t="s">
         <v>102</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="28">
-        <v>2</v>
-      </c>
-      <c r="H5" s="28">
-        <v>3</v>
-      </c>
-      <c r="I5" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E5" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
         <v>9</v>
       </c>
@@ -1108,23 +1110,23 @@
       <c r="D6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="41">
         <v>1</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="42">
         <v>1</v>
       </c>
-      <c r="G6" s="28">
-        <v>2</v>
-      </c>
-      <c r="H6" s="28">
-        <v>2</v>
-      </c>
-      <c r="I6" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G6" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
         <v>9</v>
       </c>
@@ -1137,81 +1139,81 @@
       <c r="D7" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="41">
         <v>1</v>
       </c>
-      <c r="F7" s="28">
-        <v>2</v>
-      </c>
-      <c r="G7" s="28">
-        <v>3</v>
-      </c>
-      <c r="H7" s="28">
-        <v>3</v>
-      </c>
-      <c r="I7" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="F7" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="40" t="s">
         <v>100</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="E8" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="28">
-        <v>3</v>
-      </c>
-      <c r="I8" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E8" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="40" t="s">
         <v>101</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="29" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="E9" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
         <v>9</v>
       </c>
@@ -1224,23 +1226,23 @@
       <c r="D10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="41">
         <v>0</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="42">
         <v>0</v>
       </c>
-      <c r="G10" s="28">
-        <v>2</v>
-      </c>
-      <c r="H10" s="28">
-        <v>2</v>
-      </c>
-      <c r="I10" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G10" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="25" t="s">
         <v>9</v>
       </c>
@@ -1253,23 +1255,23 @@
       <c r="D11" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="41">
         <v>0</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="42">
         <v>0</v>
       </c>
-      <c r="G11" s="28">
-        <v>2</v>
-      </c>
-      <c r="H11" s="28">
-        <v>2</v>
-      </c>
-      <c r="I11" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G11" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="25" t="s">
         <v>28</v>
       </c>
@@ -1282,14 +1284,14 @@
       <c r="D12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="27">
-        <v>2</v>
-      </c>
-      <c r="F12" s="27">
-        <v>2</v>
-      </c>
-      <c r="G12" s="27">
-        <v>2</v>
+      <c r="E12" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="41" t="s">
+        <v>36</v>
       </c>
       <c r="H12" s="26" t="s">
         <v>31</v>
@@ -1298,7 +1300,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="25" t="s">
         <v>9</v>
       </c>
@@ -1311,14 +1313,14 @@
       <c r="D13" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="27">
-        <v>2</v>
-      </c>
-      <c r="F13" s="27">
-        <v>2</v>
-      </c>
-      <c r="G13" s="27">
-        <v>2</v>
+      <c r="E13" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="41" t="s">
+        <v>36</v>
       </c>
       <c r="H13" s="26" t="s">
         <v>31</v>
@@ -1327,36 +1329,36 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="40" t="s">
         <v>18</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="H14" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="28" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E14" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="25" t="s">
         <v>9</v>
       </c>
@@ -1369,23 +1371,23 @@
       <c r="D15" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="41">
         <v>1</v>
       </c>
-      <c r="F15" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" s="28">
-        <v>2</v>
-      </c>
-      <c r="I15" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="F15" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A16" s="25" t="s">
         <v>9</v>
       </c>
@@ -1398,23 +1400,23 @@
       <c r="D16" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="41">
         <v>0</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="42">
         <v>0</v>
       </c>
-      <c r="G16" s="28">
-        <v>1</v>
-      </c>
-      <c r="H16" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" s="28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G16" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="25" t="s">
         <v>9</v>
       </c>
@@ -1427,628 +1429,628 @@
       <c r="D17" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="42">
         <v>2</v>
       </c>
-      <c r="F17" s="28">
-        <v>2</v>
-      </c>
-      <c r="G17" s="28">
-        <v>3</v>
-      </c>
-      <c r="H17" s="28">
-        <v>3</v>
-      </c>
-      <c r="I17" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="G17" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17" s="42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A18" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="27" t="s">
         <v>45</v>
       </c>
       <c r="D18" s="10"/>
-      <c r="E18" s="27">
-        <v>2</v>
-      </c>
-      <c r="F18" s="27">
-        <v>2</v>
-      </c>
-      <c r="G18" s="28">
-        <v>3</v>
-      </c>
-      <c r="H18" s="28">
-        <v>3</v>
-      </c>
-      <c r="I18" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="E18" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I18" s="42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A19" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="27" t="s">
         <v>46</v>
       </c>
       <c r="D19" s="10"/>
-      <c r="E19" s="27">
+      <c r="E19" s="41">
         <v>0</v>
       </c>
-      <c r="F19" s="28">
-        <v>0</v>
-      </c>
-      <c r="G19" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="H19" s="28">
-        <v>2</v>
-      </c>
-      <c r="I19" s="28" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F19" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="28" t="s">
         <v>47</v>
       </c>
       <c r="D20" s="10"/>
-      <c r="E20" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="28">
-        <v>3</v>
-      </c>
-      <c r="H20" s="28">
-        <v>3</v>
-      </c>
-      <c r="I20" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E20" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" s="42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="27" t="s">
         <v>48</v>
       </c>
       <c r="D21" s="10"/>
-      <c r="E21" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="28">
-        <v>3</v>
-      </c>
-      <c r="H21" s="28">
-        <v>3</v>
-      </c>
-      <c r="I21" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E21" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="27" t="s">
         <v>49</v>
       </c>
       <c r="D22" s="10"/>
-      <c r="E22" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="F22" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="28">
-        <v>3</v>
-      </c>
-      <c r="H22" s="28">
-        <v>3</v>
-      </c>
-      <c r="I22" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E22" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I22" s="42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="29" t="s">
         <v>51</v>
       </c>
       <c r="D23" s="10"/>
-      <c r="E23" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="F23" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="28">
-        <v>3</v>
-      </c>
-      <c r="H23" s="28">
-        <v>3</v>
-      </c>
-      <c r="I23" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E23" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H23" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="25" t="s">
         <v>28</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="45" t="s">
+      <c r="C24" s="40" t="s">
         <v>52</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="41">
         <v>0</v>
       </c>
-      <c r="F24" s="28">
+      <c r="F24" s="42">
         <v>0</v>
       </c>
-      <c r="G24" s="28">
-        <v>1</v>
-      </c>
-      <c r="H24" s="28">
-        <v>1</v>
-      </c>
-      <c r="I24" s="28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G24" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C25" s="27" t="s">
         <v>55</v>
       </c>
       <c r="D25" s="10"/>
-      <c r="E25" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="27">
-        <v>2</v>
-      </c>
-      <c r="H25" s="27">
-        <v>3</v>
-      </c>
-      <c r="I25" s="27">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="E25" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="I25" s="41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="25" x14ac:dyDescent="0.35">
       <c r="A26" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="31" t="s">
+      <c r="C26" s="27" t="s">
         <v>56</v>
       </c>
       <c r="D26" s="10"/>
-      <c r="E26" s="27">
+      <c r="E26" s="41">
         <v>2</v>
       </c>
-      <c r="F26" s="27">
+      <c r="F26" s="41">
         <v>2</v>
       </c>
-      <c r="G26" s="27">
-        <v>2</v>
-      </c>
-      <c r="H26" s="27">
-        <v>2</v>
-      </c>
-      <c r="I26" s="27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G26" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="I26" s="41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="31" t="s">
+      <c r="C27" s="27" t="s">
         <v>57</v>
       </c>
       <c r="D27" s="10"/>
-      <c r="E27" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="F27" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="27">
-        <v>2</v>
-      </c>
-      <c r="H27" s="27">
-        <v>2</v>
-      </c>
-      <c r="I27" s="27" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E27" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="I27" s="41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="31" t="s">
+      <c r="C28" s="27" t="s">
         <v>58</v>
       </c>
       <c r="D28" s="10"/>
-      <c r="E28" s="27">
+      <c r="E28" s="41">
         <v>0</v>
       </c>
-      <c r="F28" s="27">
+      <c r="F28" s="41">
         <v>0</v>
       </c>
-      <c r="G28" s="27">
-        <v>1</v>
-      </c>
-      <c r="H28" s="27">
-        <v>2</v>
-      </c>
-      <c r="I28" s="27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" s="24" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="34" t="s">
+      <c r="G28" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="24" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A29" s="30" t="s">
         <v>9</v>
       </c>
       <c r="B29" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C29" s="31" t="s">
         <v>59</v>
       </c>
       <c r="D29" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="E29" s="36">
-        <v>2</v>
-      </c>
-      <c r="F29" s="36">
-        <v>2</v>
-      </c>
-      <c r="G29" s="36">
-        <v>2</v>
-      </c>
-      <c r="H29" s="36">
-        <v>2</v>
-      </c>
-      <c r="I29" s="36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="37" t="s">
+      <c r="E29" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="I29" s="41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="32" t="s">
         <v>9</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="27" t="s">
         <v>61</v>
       </c>
       <c r="D30" s="14"/>
-      <c r="E30" s="27">
+      <c r="E30" s="41">
         <v>0</v>
       </c>
-      <c r="F30" s="27">
+      <c r="F30" s="41">
         <v>0</v>
       </c>
-      <c r="G30" s="27">
-        <v>0</v>
-      </c>
-      <c r="H30" s="27">
-        <v>0</v>
-      </c>
-      <c r="I30" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="37" t="s">
+      <c r="G30" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="42" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="32" t="s">
         <v>9</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="31" t="s">
+      <c r="C31" s="27" t="s">
         <v>62</v>
       </c>
       <c r="D31" s="14"/>
-      <c r="E31" s="27">
+      <c r="E31" s="41">
         <v>2</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="41">
         <v>2</v>
       </c>
-      <c r="G31" s="27">
-        <v>2</v>
-      </c>
-      <c r="H31" s="27">
-        <v>2</v>
-      </c>
-      <c r="I31" s="27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="38" t="s">
+      <c r="G31" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="H31" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="I31" s="41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="27" t="s">
         <v>64</v>
       </c>
       <c r="D32" s="14"/>
-      <c r="E32" s="28">
+      <c r="E32" s="42">
         <v>0</v>
       </c>
-      <c r="F32" s="28">
+      <c r="F32" s="42">
         <v>0</v>
       </c>
-      <c r="G32" s="28">
-        <v>0</v>
-      </c>
-      <c r="H32" s="28">
-        <v>2</v>
-      </c>
-      <c r="I32" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="38" t="s">
+      <c r="G32" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I32" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" s="33" t="s">
         <v>28</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="31" t="s">
+      <c r="C33" s="27" t="s">
         <v>65</v>
       </c>
       <c r="D33" s="14"/>
-      <c r="E33" s="28">
+      <c r="E33" s="42">
         <v>0</v>
       </c>
-      <c r="F33" s="28">
+      <c r="F33" s="42">
         <v>0</v>
       </c>
-      <c r="G33" s="28">
-        <v>0</v>
-      </c>
-      <c r="H33" s="28">
-        <v>0</v>
-      </c>
-      <c r="I33" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="38" t="s">
+      <c r="G33" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I33" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" s="33" t="s">
         <v>28</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="31" t="s">
+      <c r="C34" s="27" t="s">
         <v>66</v>
       </c>
       <c r="D34" s="14"/>
-      <c r="E34" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="28">
-        <v>2</v>
-      </c>
-      <c r="H34" s="28">
-        <v>2</v>
-      </c>
-      <c r="I34" s="28" t="s">
+      <c r="E34" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I34" s="42" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="38" t="s">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" s="33" t="s">
         <v>28</v>
       </c>
       <c r="B35" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C35" s="31" t="s">
+      <c r="C35" s="27" t="s">
         <v>67</v>
       </c>
       <c r="D35" s="14"/>
-      <c r="E35" s="28">
+      <c r="E35" s="42">
         <v>2</v>
       </c>
-      <c r="F35" s="28">
+      <c r="F35" s="42">
         <v>2</v>
       </c>
-      <c r="G35" s="28">
-        <v>2</v>
-      </c>
-      <c r="H35" s="28">
-        <v>2</v>
-      </c>
-      <c r="I35" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="39" t="s">
+      <c r="G35" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H35" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I35" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="34" t="s">
         <v>28</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C36" s="31" t="s">
+      <c r="C36" s="27" t="s">
         <v>68</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="E36" s="28">
-        <v>2</v>
-      </c>
-      <c r="F36" s="28">
-        <v>2</v>
-      </c>
-      <c r="G36" s="28">
-        <v>2</v>
-      </c>
-      <c r="H36" s="28">
-        <v>2</v>
-      </c>
-      <c r="I36" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="39" t="s">
+      <c r="E36" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I36" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A37" s="34" t="s">
         <v>28</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C37" s="31" t="s">
+      <c r="C37" s="27" t="s">
         <v>70</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E37" s="28">
-        <v>2</v>
-      </c>
-      <c r="F37" s="28">
-        <v>2</v>
-      </c>
-      <c r="G37" s="28">
-        <v>2</v>
-      </c>
-      <c r="H37" s="28">
-        <v>2</v>
-      </c>
-      <c r="I37" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="38" t="s">
+      <c r="E37" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I37" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" s="33" t="s">
         <v>28</v>
       </c>
       <c r="B38" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C38" s="31" t="s">
+      <c r="C38" s="27" t="s">
         <v>72</v>
       </c>
       <c r="D38" s="14"/>
-      <c r="E38" s="28">
-        <v>2</v>
-      </c>
-      <c r="F38" s="28">
-        <v>2</v>
-      </c>
-      <c r="G38" s="28">
-        <v>2</v>
-      </c>
-      <c r="H38" s="28">
-        <v>2</v>
-      </c>
-      <c r="I38" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="38" t="s">
+      <c r="E38" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H38" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I38" s="42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B39" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C39" s="31" t="s">
+      <c r="C39" s="27" t="s">
         <v>74</v>
       </c>
       <c r="D39" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E39" s="28">
+      <c r="E39" s="42">
         <v>0</v>
       </c>
-      <c r="F39" s="28">
+      <c r="F39" s="42">
         <v>0</v>
       </c>
-      <c r="G39" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="I39" s="28" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="38" t="s">
+      <c r="G39" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B40" s="13" t="s">
@@ -2058,24 +2060,24 @@
         <v>76</v>
       </c>
       <c r="D40" s="14"/>
-      <c r="E40" s="28">
+      <c r="E40" s="42">
         <v>0</v>
       </c>
-      <c r="F40" s="28">
+      <c r="F40" s="42">
         <v>0</v>
       </c>
-      <c r="G40" s="28">
-        <v>1</v>
-      </c>
-      <c r="H40" s="28">
-        <v>1</v>
-      </c>
-      <c r="I40" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="38" t="s">
+      <c r="G40" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I40" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B41" s="13" t="s">
@@ -2085,324 +2087,324 @@
         <v>77</v>
       </c>
       <c r="D41" s="14"/>
-      <c r="E41" s="28">
+      <c r="E41" s="42">
         <v>0</v>
       </c>
-      <c r="F41" s="28">
+      <c r="F41" s="42">
         <v>0</v>
       </c>
-      <c r="G41" s="28">
-        <v>1</v>
-      </c>
-      <c r="H41" s="28">
-        <v>1</v>
-      </c>
-      <c r="I41" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="38" t="s">
+      <c r="G41" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="31" t="s">
+      <c r="C42" s="27" t="s">
         <v>99</v>
       </c>
       <c r="D42" s="14"/>
-      <c r="E42" s="28">
+      <c r="E42" s="42">
         <v>0</v>
       </c>
-      <c r="F42" s="28">
-        <v>0</v>
-      </c>
-      <c r="G42" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="H42" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="I42" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="38" t="s">
+      <c r="F42" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="H42" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I42" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="C43" s="40" t="s">
+      <c r="C43" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="D43" s="31" t="s">
+      <c r="D43" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="E43" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="F43" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G43" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="H43" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="I43" s="28" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="38" t="s">
+      <c r="E43" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="F43" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B44" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="C44" s="41" t="s">
+      <c r="C44" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="D44" s="31"/>
-      <c r="E44" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="F44" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="H44" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="I44" s="29" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="38" t="s">
+      <c r="D44" s="27"/>
+      <c r="E44" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B45" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="C45" s="41" t="s">
+      <c r="C45" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="D45" s="31"/>
-      <c r="E45" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="F45" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="G45" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="H45" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="I45" s="29" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="38" t="s">
+      <c r="D45" s="27"/>
+      <c r="E45" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B46" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="C46" s="41" t="s">
+      <c r="C46" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="D46" s="31" t="s">
+      <c r="D46" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="E46" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="F46" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="G46" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="H46" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="I46" s="29" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="38" t="s">
+      <c r="E46" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B47" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C47" s="31" t="s">
+      <c r="C47" s="27" t="s">
         <v>82</v>
       </c>
       <c r="D47" s="14"/>
-      <c r="E47" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="F47" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="G47" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H47" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="I47" s="28" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="42" t="s">
+      <c r="E47" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="H47" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" s="42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="37" t="s">
         <v>9</v>
       </c>
       <c r="B48" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C48" s="43" t="s">
+      <c r="C48" s="38" t="s">
         <v>84</v>
       </c>
       <c r="D48" s="17"/>
-      <c r="E48" s="44" t="s">
-        <v>20</v>
-      </c>
-      <c r="F48" s="44" t="s">
-        <v>13</v>
-      </c>
-      <c r="G48" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="H48" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="I48" s="44" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="42" t="s">
+      <c r="E48" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="I48" s="43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="37" t="s">
         <v>9</v>
       </c>
       <c r="B49" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C49" s="43" t="s">
+      <c r="C49" s="38" t="s">
         <v>85</v>
       </c>
       <c r="D49" s="17"/>
-      <c r="E49" s="44" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="44" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="H49" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="I49" s="44" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="42" t="s">
+      <c r="E49" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="I49" s="43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="37" t="s">
         <v>9</v>
       </c>
       <c r="B50" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C50" s="43" t="s">
+      <c r="C50" s="38" t="s">
         <v>87</v>
       </c>
       <c r="D50" s="17"/>
-      <c r="E50" s="44" t="s">
-        <v>20</v>
-      </c>
-      <c r="F50" s="44" t="s">
-        <v>20</v>
-      </c>
-      <c r="G50" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="H50" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="I50" s="44" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="42" t="s">
+      <c r="E50" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F50" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I50" s="43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="37" t="s">
         <v>9</v>
       </c>
       <c r="B51" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C51" s="43" t="s">
+      <c r="C51" s="38" t="s">
         <v>88</v>
       </c>
       <c r="D51" s="17"/>
-      <c r="E51" s="44" t="s">
-        <v>20</v>
-      </c>
-      <c r="F51" s="44" t="s">
-        <v>20</v>
-      </c>
-      <c r="G51" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="H51" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="I51" s="44" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="42" t="s">
+      <c r="E51" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F51" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="I51" s="43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="37" t="s">
         <v>9</v>
       </c>
       <c r="B52" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C52" s="43" t="s">
+      <c r="C52" s="38" t="s">
         <v>89</v>
       </c>
       <c r="D52" s="17"/>
-      <c r="E52" s="44" t="s">
-        <v>20</v>
-      </c>
-      <c r="F52" s="44" t="s">
-        <v>20</v>
-      </c>
-      <c r="G52" s="44" t="s">
-        <v>13</v>
-      </c>
-      <c r="H52" s="44" t="s">
-        <v>13</v>
-      </c>
-      <c r="I52" s="44" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E52" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F52" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="G52" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="I52" s="43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="15"/>
       <c r="B54" s="11"/>
       <c r="C54" s="18"/>
